--- a/output/Data and Chart Outputs/singapore_gas.xlsx
+++ b/output/Data and Chart Outputs/singapore_gas.xlsx
@@ -6037,7 +6037,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Jan-06 only (part-year)</t>
+          <t>Jan-Jun only (part-year)</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/singapore_gas.xlsx
+++ b/output/Data and Chart Outputs/singapore_gas.xlsx
@@ -168,6 +168,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -352,7 +353,7 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="yyyy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -384,6 +385,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -392,6 +394,7 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -422,6 +425,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -494,7 +498,7 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="yyyy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -526,6 +530,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -534,6 +539,7 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -564,6 +570,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -613,7 +620,7 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -645,15 +652,13 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -683,6 +688,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -755,7 +761,7 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -787,6 +793,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -795,6 +802,7 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>

--- a/output/Data and Chart Outputs/singapore_gas.xlsx
+++ b/output/Data and Chart Outputs/singapore_gas.xlsx
@@ -26,9 +26,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -68,13 +69,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -358,6 +357,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
@@ -391,6 +402,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -503,6 +520,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
@@ -536,6 +565,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -625,6 +660,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -658,6 +705,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -766,6 +819,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="3"/>
@@ -799,6 +864,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -1261,6 +1332,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -1275,6 +1347,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -1310,6 +1383,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
@@ -3635,7 +3709,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="B2" t="n">
@@ -3658,7 +3732,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B3" t="n">
@@ -3681,7 +3755,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B4" t="n">
@@ -3704,7 +3778,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B5" t="n">
@@ -3727,7 +3801,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B6" t="n">
@@ -3750,7 +3824,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B7" t="n">
@@ -3773,7 +3847,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="B8" t="n">
@@ -3796,7 +3870,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B9" t="n">
@@ -3819,7 +3893,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="B10" t="n">
@@ -3842,7 +3916,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="B11" t="n">
@@ -3865,7 +3939,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="B12" t="n">
@@ -3888,7 +3962,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="B13" t="n">
@@ -3911,7 +3985,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B14" t="n">
@@ -3934,7 +4008,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B15" t="n">
@@ -3957,7 +4031,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B16" t="n">
@@ -3980,7 +4054,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B17" t="n">
@@ -4038,7 +4112,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="n">
@@ -4049,7 +4123,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>38718</v>
       </c>
       <c r="B3" t="n">
@@ -4060,7 +4134,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>39083</v>
       </c>
       <c r="B4" t="n">
@@ -4071,7 +4145,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>39448</v>
       </c>
       <c r="B5" t="n">
@@ -4082,7 +4156,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="B6" t="n">
@@ -4093,7 +4167,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B7" t="n">
@@ -4104,7 +4178,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B8" t="n">
@@ -4115,7 +4189,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B9" t="n">
@@ -4126,7 +4200,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B10" t="n">
@@ -4137,7 +4211,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B11" t="n">
@@ -4148,7 +4222,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="B12" t="n">
@@ -4159,7 +4233,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B13" t="n">
@@ -4170,7 +4244,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="B14" t="n">
@@ -4181,7 +4255,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="B15" t="n">
@@ -4192,7 +4266,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="B16" t="n">
@@ -4203,7 +4277,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="B17" t="n">
@@ -4214,7 +4288,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B18" t="n">
@@ -4225,7 +4299,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B19" t="n">
@@ -4236,7 +4310,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B20" t="n">
@@ -4247,7 +4321,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B21" t="n">
@@ -4288,7 +4362,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -4296,7 +4370,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -4304,7 +4378,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -4312,7 +4386,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -4320,7 +4394,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -4328,7 +4402,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -4336,7 +4410,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -4344,7 +4418,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -4352,7 +4426,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -4360,7 +4434,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -4368,7 +4442,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -4376,7 +4450,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -4384,7 +4458,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -4392,7 +4466,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -4400,7 +4474,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -4408,7 +4482,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -4416,7 +4490,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -4424,7 +4498,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -4432,7 +4506,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -4440,7 +4514,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -4448,7 +4522,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -4456,7 +4530,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -4464,7 +4538,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -4472,7 +4546,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -4480,7 +4554,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -4488,7 +4562,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -4496,7 +4570,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -4504,7 +4578,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -4512,7 +4586,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -4520,7 +4594,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -4528,7 +4602,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -4536,7 +4610,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -4544,7 +4618,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -4552,7 +4626,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -4560,7 +4634,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -4568,7 +4642,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -4576,7 +4650,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -4584,7 +4658,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -4592,7 +4666,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -4600,7 +4674,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -4608,7 +4682,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -4616,7 +4690,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -4624,7 +4698,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -4632,7 +4706,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -4640,7 +4714,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -4648,7 +4722,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -4656,7 +4730,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -4664,7 +4738,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -4672,7 +4746,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -4680,7 +4754,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -4688,7 +4762,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -4696,7 +4770,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -4704,7 +4778,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -4712,7 +4786,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -4720,7 +4794,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -4728,7 +4802,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -4736,7 +4810,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -4744,7 +4818,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -4752,7 +4826,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -4760,7 +4834,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -4768,7 +4842,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -4776,7 +4850,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -4784,7 +4858,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -4792,7 +4866,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -4800,7 +4874,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -4808,7 +4882,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -4816,7 +4890,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -4824,7 +4898,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -4867,7 +4941,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>42005</v>
       </c>
       <c r="B2" t="n">
@@ -4878,7 +4952,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>42095</v>
       </c>
       <c r="B3" t="n">
@@ -4889,7 +4963,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>42186</v>
       </c>
       <c r="B4" t="n">
@@ -4900,7 +4974,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>42278</v>
       </c>
       <c r="B5" t="n">
@@ -4911,7 +4985,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>42370</v>
       </c>
       <c r="B6" t="n">
@@ -4922,7 +4996,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>42461</v>
       </c>
       <c r="B7" t="n">
@@ -4933,7 +5007,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>42552</v>
       </c>
       <c r="B8" t="n">
@@ -4944,7 +5018,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>42644</v>
       </c>
       <c r="B9" t="n">
@@ -4955,7 +5029,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>42736</v>
       </c>
       <c r="B10" t="n">
@@ -4966,7 +5040,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>42826</v>
       </c>
       <c r="B11" t="n">
@@ -4977,7 +5051,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>42917</v>
       </c>
       <c r="B12" t="n">
@@ -4988,7 +5062,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>43009</v>
       </c>
       <c r="B13" t="n">
@@ -4999,7 +5073,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>43101</v>
       </c>
       <c r="B14" t="n">
@@ -5010,7 +5084,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>43191</v>
       </c>
       <c r="B15" t="n">
@@ -5021,7 +5095,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>43282</v>
       </c>
       <c r="B16" t="n">
@@ -5032,7 +5106,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>43374</v>
       </c>
       <c r="B17" t="n">
@@ -5043,7 +5117,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>43466</v>
       </c>
       <c r="B18" t="n">
@@ -5054,7 +5128,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>43556</v>
       </c>
       <c r="B19" t="n">
@@ -5065,7 +5139,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>43647</v>
       </c>
       <c r="B20" t="n">
@@ -5076,7 +5150,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="B21" t="n">
@@ -5087,7 +5161,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>43831</v>
       </c>
       <c r="B22" t="n">
@@ -5098,7 +5172,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>43922</v>
       </c>
       <c r="B23" t="n">
@@ -5109,7 +5183,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44013</v>
       </c>
       <c r="B24" t="n">
@@ -5120,7 +5194,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44105</v>
       </c>
       <c r="B25" t="n">
@@ -5131,7 +5205,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B26" t="n">
@@ -5142,7 +5216,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B27" t="n">
@@ -5153,7 +5227,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B28" t="n">
@@ -5164,7 +5238,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B29" t="n">
@@ -5175,7 +5249,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B30" t="n">
@@ -5186,7 +5260,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B31" t="n">
@@ -5197,7 +5271,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B32" t="n">
@@ -5208,7 +5282,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B33" t="n">
@@ -5219,7 +5293,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B34" t="n">
@@ -5230,7 +5304,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B35" t="n">
@@ -5241,7 +5315,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B36" t="n">
@@ -5252,7 +5326,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B37" t="n">
@@ -5263,7 +5337,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -5274,7 +5348,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B39" t="n">
@@ -5285,7 +5359,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B40" t="n">
@@ -5296,7 +5370,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B41" t="n">
@@ -5307,7 +5381,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B42" t="n">
@@ -5318,7 +5392,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B43" t="n">
@@ -5329,7 +5403,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B44" t="n">
@@ -5340,7 +5414,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B45" t="n">
@@ -5351,7 +5425,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B46" t="n">
@@ -5362,7 +5436,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B47" t="n">

--- a/output/Data and Chart Outputs/singapore_gas.xlsx
+++ b/output/Data and Chart Outputs/singapore_gas.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Imports" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Power burn" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Power burn daily" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Town gas" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Annual demand by sector" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Annual imports" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final consumption by subsector" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power burn monthly (est)" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power burn daily (est)" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calibration" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Town gas quarterly" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Chart - Imports" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Chart - Power burn" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Chart - Power burn daily" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Chart - Town gas" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Annual demand by sector" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Annual imports" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Final consumption by subsector" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Power burn monthly (est)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Power burn daily (est)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Calibration" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Town gas quarterly" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -155,17 +155,18 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Singapore natural gas demand by sector (to 2024)</a:t>
             </a:r>
           </a:p>
@@ -186,10 +187,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -214,10 +215,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -242,10 +243,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -270,10 +271,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EDA100"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -298,10 +299,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="E87BA4"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -326,10 +327,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="008300"/>
+            <a:solidFill>
+              <a:srgbClr val="9A9A9A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -362,8 +363,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -389,8 +390,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -407,7 +408,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -421,7 +422,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -430,17 +431,18 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Singapore natural gas imports, pipeline vs LNG (to 2024)</a:t>
             </a:r>
           </a:p>
@@ -461,10 +463,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -489,10 +491,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -525,8 +527,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -552,8 +554,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -570,7 +572,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -584,7 +586,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -593,17 +595,18 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Singapore gas burn for power, estimated from metered CCGT generation (to Aug/26)</a:t>
             </a:r>
           </a:p>
@@ -623,7 +626,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+            <a:ln w="22225">
               <a:solidFill>
                 <a:srgbClr val="2A78D6"/>
               </a:solidFill>
@@ -633,7 +636,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -665,8 +668,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -692,8 +695,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -710,7 +713,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -720,7 +723,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -729,17 +732,18 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Singapore gas burn for power, daily, estimated from metered CCGT generation (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -759,7 +763,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+            <a:ln w="22225">
               <a:solidFill>
                 <a:srgbClr val="2A78D6"/>
               </a:solidFill>
@@ -769,7 +773,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -795,7 +799,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+            <a:ln w="22225">
               <a:solidFill>
                 <a:srgbClr val="EB6834"/>
               </a:solidFill>
@@ -805,7 +809,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -837,8 +841,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -864,8 +868,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -882,7 +886,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -896,7 +900,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -905,17 +909,18 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Singapore town gas sales (to Apr/26)</a:t>
             </a:r>
           </a:p>
@@ -936,10 +941,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -964,10 +969,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1000,8 +1005,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1027,8 +1032,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1045,7 +1050,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1059,7 +1064,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1068,7 +1073,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>8</col>
@@ -1083,9 +1088,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1095,7 +1100,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -1110,9 +1115,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1122,7 +1127,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -1137,9 +1142,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1149,7 +1154,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -1164,9 +1169,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1176,7 +1181,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -1191,9 +1196,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
